--- a/data/flux/paper_code_data/source_data/Fig5_residual_by_mortality_class.xlsx
+++ b/data/flux/paper_code_data/source_data/Fig5_residual_by_mortality_class.xlsx
@@ -22,13 +22,13 @@
     <t>note</t>
   </si>
   <si>
-    <t>Fig. 5: mean residual (observed - predicted) per class of the site-year's total mortality, without (C+T) and with mortality (C+T+M), AutoGluon, 24 months.</t>
+    <t>Fig. 5: mean residual (observed - predicted) per class of the site-year's relative mortality, without (C+T) and with mortality (C+T+M), AutoGluon, 24 months.</t>
   </si>
   <si>
     <t>residual_by_class: mean and 95 % site-block bootstrap interval; correction_by_class: residual(C+T+M) - residual(C+T) with one-sided paired permutation (BH);</t>
   </si>
   <si>
-    <t>correction_trend: mixed-model slope of the correction per +10 % total mortality with site-block bootstrap.</t>
+    <t>correction_trend: mixed-model slope of the correction per +10 % relative mortality with site-block bootstrap.</t>
   </si>
   <si>
     <t>response</t>
